--- a/data/trans_bre/IP16A05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 4,58</t>
+          <t>-19,34; 4,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 19,82</t>
+          <t>-8,48; 18,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 17,47</t>
+          <t>-16,12; 18,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 38,45</t>
+          <t>5,54; 39,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 149,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,5; 331,8</t>
+          <t>-45,57; 312,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 183,19</t>
+          <t>-60,26; 214,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 11,42</t>
+          <t>-10,64; 11,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 14,84</t>
+          <t>-8,6; 14,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 14,33</t>
+          <t>-10,07; 13,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 22,35</t>
+          <t>-8,42; 21,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,37; 145,85</t>
+          <t>-56,29; 135,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,66; 137,89</t>
+          <t>-43,13; 126,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,01; 217,98</t>
+          <t>-58,93; 206,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,7; 364,28</t>
+          <t>-57,72; 376,08</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 6,1</t>
+          <t>-20,04; 6,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 20,5</t>
+          <t>-11,21; 20,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 2,09</t>
+          <t>-20,61; 1,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 11,97</t>
+          <t>-8,41; 12,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 292,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-63,59; 611,28</t>
+          <t>-64,27; 465,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-94,19; 116,28</t>
+          <t>-100,0; 42,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-77,79; —</t>
+          <t>-81,33; —</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 14,6</t>
+          <t>-3,45; 13,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 26,69</t>
+          <t>-1,15; 24,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 15,29</t>
+          <t>-10,35; 14,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,27</t>
+          <t>-2,3; 4,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,95; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 4,1</t>
+          <t>-7,1; 4,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 12,27</t>
+          <t>-1,72; 11,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 5,05</t>
+          <t>-7,44; 6,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 8,97</t>
+          <t>-2,34; 9,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 55,95</t>
+          <t>-55,29; 58,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 122,81</t>
+          <t>-12,74; 110,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 57,54</t>
+          <t>-47,42; 70,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 250,83</t>
+          <t>-35,55; 262,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 4,42</t>
+          <t>-19,33; 3,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 18,66</t>
+          <t>-7,52; 19,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 18,2</t>
+          <t>-16,55; 18,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 39,1</t>
+          <t>6,24; 37,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,75</t>
+          <t>-100,0; 121,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 312,64</t>
+          <t>-43,89; 343,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,26; 214,71</t>
+          <t>-59,94; 194,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 11,51</t>
+          <t>-10,42; 11,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 14,88</t>
+          <t>-8,4; 15,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 13,51</t>
+          <t>-9,56; 14,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 21,21</t>
+          <t>-8,63; 21,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,29; 135,4</t>
+          <t>-56,85; 143,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 126,02</t>
+          <t>-41,51; 129,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,93; 206,66</t>
+          <t>-55,74; 224,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 376,08</t>
+          <t>-57,68; 294,95</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 6,18</t>
+          <t>-20,27; 5,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 20,82</t>
+          <t>-11,66; 20,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 1,09</t>
+          <t>-20,95; 2,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 12,41</t>
+          <t>-9,03; 11,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 292,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,27; 465,34</t>
+          <t>-68,67; 463,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,48</t>
+          <t>-94,54; 66,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,33; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 13,94</t>
+          <t>-4,23; 13,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 24,48</t>
+          <t>-0,64; 25,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 14,55</t>
+          <t>-10,22; 14,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,41</t>
+          <t>-2,76; 3,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-58,98; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,3</t>
+          <t>-7,11; 4,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 11,24</t>
+          <t>-1,7; 11,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 6,3</t>
+          <t>-7,98; 5,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 9,35</t>
+          <t>-2,05; 9,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,29; 58,6</t>
+          <t>-54,61; 58,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 110,81</t>
+          <t>-11,11; 118,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 70,09</t>
+          <t>-47,57; 62,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 262,05</t>
+          <t>-31,22; 280,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumieron medicamentos antibióticos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,92</t>
+          <t>20,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>994,55%</t>
+          <t>1035,2%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 3,71</t>
+          <t>-19,19; 4,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 19,75</t>
+          <t>-8,17; 19,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 18,17</t>
+          <t>-16,14; 17,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 37,75</t>
+          <t>5,48; 40,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,89; 343,95</t>
+          <t>-48,5; 331,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-59,94; 194,56</t>
+          <t>-59,95; 183,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,84</t>
+          <t>-1,87</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>-15,53%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 11,54</t>
+          <t>-11,1; 11,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 15,43</t>
+          <t>-9,39; 14,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 14,26</t>
+          <t>-9,1; 14,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 21,1</t>
+          <t>-13,15; 7,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,85; 143,21</t>
+          <t>-57,37; 145,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,51; 129,64</t>
+          <t>-43,66; 137,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,74; 224,45</t>
+          <t>-55,01; 217,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 294,95</t>
+          <t>-72,51; 129,0</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 5,93</t>
+          <t>-20,26; 6,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 20,96</t>
+          <t>-10,98; 20,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 2,23</t>
+          <t>-20,91; 2,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 11,25</t>
+          <t>-7,8; 12,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,67; 463,1</t>
+          <t>-63,59; 611,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-94,54; 66,58</t>
+          <t>-94,19; 116,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,64; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>173,97%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 13,17</t>
+          <t>-3,21; 14,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 25,62</t>
+          <t>-1,21; 26,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 14,49</t>
+          <t>-10,14; 15,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,97</t>
+          <t>-1,05; 7,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,98; —</t>
+          <t>-50,95; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 4,15</t>
+          <t>-7,03; 4,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 11,68</t>
+          <t>-1,44; 12,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 5,69</t>
+          <t>-7,9; 5,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 9,4</t>
+          <t>-2,1; 7,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 58,83</t>
+          <t>-54,63; 55,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 118,22</t>
+          <t>-10,51; 122,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 62,0</t>
+          <t>-49,64; 57,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 280,6</t>
+          <t>-30,09; 227,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-5,86</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20,16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-49,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1035,2%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.255462113725075</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.110204292285627</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.3530328136596477</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.34276930807088</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.4314700651544354</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.3331375126012007</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.09496939369794841</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>7.951642292668364</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-19,19; 4,58</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,17; 19,82</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-16,14; 17,47</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5,48; 40,01</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-48,5; 331,8</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-59,95; 183,19</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.623369512090991</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.321726255381198</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.422540137176465</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.050537728111908</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.5359806321402546</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6214517095022041</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.710930009926579</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.513461586195799</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.442096095904431</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>12.19807400944206</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>2.710315841619882</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3.041503191915409</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,26</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,87</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-15,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-11,1; 11,42</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-9,39; 14,84</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,1; 14,33</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-13,15; 7,34</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-57,37; 145,85</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-43,66; 137,89</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-55,01; 217,98</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-72,51; 129,0</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.392329400400071</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.3412799277222739</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8733653417499723</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3066361196809153</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1396865797530478</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.08284980689872526</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.419907168286455</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.09665195152300089</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,77</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-8,81</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-50,06%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-64,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>25,99%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.455808636067164</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.634666543400951</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.465871318930744</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.427782457295212</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6331382727715864</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4996916111477495</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4692712862761432</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7295150334145434</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-20,26; 6,1</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,98; 20,5</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-20,91; 2,09</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,8; 12,2</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-63,59; 611,28</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-94,19; 116,28</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-80,64; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.875121493073512</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.459319350379571</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.320556974191225</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.400205307259276</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.224683026121679</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.30838819762336</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2.842214445276112</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.701742766964134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +811,275 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,27</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10,62</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>101,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>207,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>173,97%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.9282455876866812</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.136462762528843</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.49481359992489</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.3788537391208741</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.4774987062807952</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.5485150385237689</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.6180178704439303</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.2520065380432778</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,21; 14,6</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,21; 26,69</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-10,14; 15,29</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,05; 7,62</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-50,95; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.710782021976095</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.909721857262452</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.141593797769137</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.049006879694038</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.6485731127973553</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.113619522613966</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.388650613242515</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3337095938435317</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.861095339944484</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>7.661880589230446</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5650851735449224</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.405326452654261</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.785696608169516</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.03862880307033516</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.3132197825486363</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.6564572967156361</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2.51072579394151</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.04441419406147875</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1.506596111997562</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.8880908980471207</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.01398635800535264</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.723543664927998</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.2331241591724804</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.7679879887636504</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.04450529027347</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.280115380275019</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.856794031010512</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.391059247046905</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,91</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-12,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-10,28%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-7,03; 4,1</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,44; 12,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-7,9; 5,05</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 7,83</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-54,63; 55,95</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-10,51; 122,81</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-49,64; 57,54</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-30,09; 227,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.3935494938689252</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.983974345583465</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.04114815518994029</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.6209154895944783</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1937165461528148</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.3612848422709916</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.01908667176998525</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.4866226165491471</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.535960186514303</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.6402136029516783</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.224466549254025</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.509848395882897</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5805646871208628</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2092512475285082</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4424791810761384</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3216714147355654</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.725843034869579</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.46752277807275</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.172567130902131</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.788997790296643</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.4961060528826097</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.199654600483328</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.8146357680153501</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>2.311469162961169</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1087,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
